--- a/Outputs/PtX_demand_EE.xlsx
+++ b/Outputs/PtX_demand_EE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>9.082503198971148e-05</v>
-      </c>
+      <c r="D2" t="n">
+        <v>0.0002346845765005068</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0001754969404269362</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>1.1449655537161e-10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.850652176654432e-05</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -522,17 +520,23 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>9.082503198971148e-05</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1.1449655537161e-10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.850652176654432e-05</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -551,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -570,7 +574,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -578,24 +582,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>5.951987479243202e-05</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.730757205598769e-05</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>7.693194052591921e-06</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -603,14 +601,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>5.951987479243202e-05</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.0003497013861488061</v>
+        <v>2.730757205598769e-05</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>3.436751862763012e-05</v>
+        <v>7.693194052591921e-06</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -618,7 +618,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -627,17 +627,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0003497013861488061</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>3.436751862763012e-05</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -646,29 +650,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.001636165311418535</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.882606390480593e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0003132736250606</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0016392156151277</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.556733278696332e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.002177464365623002</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -678,28 +670,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.01617614087513679</v>
+        <v>0.001636165311418535</v>
       </c>
       <c r="G10" t="n">
-        <v>4.142947176255379e-05</v>
+        <v>5.882606390480593e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.002863152017891</v>
+        <v>0.0003132736250606</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0102584426004798</v>
+        <v>0.0016392156151277</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002152891401867</v>
+        <v>3.556733278696332e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02132334971103646</v>
+        <v>0.002177464365623002</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -707,20 +699,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.0002970049348188396</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.01617614087513679</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.142947176255379e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.002863152017891</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0102584426004798</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0002152891401867</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02132334971103646</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -729,7 +731,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0001076404163676046</v>
+        <v>0.0002970049348188396</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -741,7 +743,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -750,83 +752,87 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.0004641652259788762</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.01828014017674983</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4.731207815303437e-05</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.003176425757448155</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.01198822545005427</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0002508564729736633</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.02350081407665946</v>
-      </c>
+        <v>0.00150444262044033</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.0004366967881524865</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.0001076404163676046</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>9.584626307956239e-09</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6.881349660176644e-05</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0.0002346845765005068</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.002144104786846142</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.01828014017674983</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.731207815303437e-05</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.003176425757448155</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01198822545005427</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0002508564729736633</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.02350081407665946</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0.000227793562643079</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0001755096120484775</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -837,7 +843,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -847,12 +853,14 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>1.594077719567545e-10</v>
+        <v>0.0004366967881524865</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>9.584626307956239e-09</v>
+      </c>
       <c r="I17" t="n">
-        <v>2.065273219980239e-11</v>
+        <v>6.881349660176644e-05</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -860,7 +868,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -868,24 +876,18 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.0002367686394466318</v>
-      </c>
-      <c r="F18" t="n">
-        <v>3.37213248451954e-05</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>1.41983412411986e-05</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -894,21 +896,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.0001890745293606341</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>3.621938182632187e-05</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -917,17 +915,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>1.594077719567545e-10</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>2.065273219980239e-11</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -935,30 +937,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.0002367686394466318</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.0007047696184429826</v>
-      </c>
-      <c r="G21" t="n">
-        <v>9.589618898468852e-06</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0003813658689076</v>
-      </c>
+        <v>3.37213248451954e-05</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0010709142162089</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.320853681627712e-05</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.002463983516709142</v>
-      </c>
+        <v>1.41983412411986e-05</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -968,28 +964,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.00436006402907351</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4.453898550539274e-05</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.0026994173542879</v>
-      </c>
+        <v>0.0001890745293606341</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.0045305831688898</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.0001910498510613</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.02068552430275745</v>
-      </c>
+        <v>3.621938182632187e-05</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -997,9 +985,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.000295424140406074</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1010,7 +996,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1018,20 +1004,30 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.0004265001570010997</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.0007047696184429826</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9.589618898468852e-06</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0003813658689076</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0010709142162089</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.320853681627712e-05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.002463983516709142</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1039,65 +1035,61 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>0.0009586929368538056</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.005724326449282582</v>
+        <v>0.00436006402907351</v>
       </c>
       <c r="G25" t="n">
-        <v>5.412860440386159e-05</v>
+        <v>4.453898550539274e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.003080792807821808</v>
+        <v>0.0026994173542879</v>
       </c>
       <c r="I25" t="n">
-        <v>0.00572072862542072</v>
+        <v>0.0045305831688898</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0002342583878775771</v>
+        <v>0.0001910498510613</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02314950781946659</v>
+        <v>0.02068552430275745</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0006056041171712137</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.000295424140406074</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>1.624516956572593e-08</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0001092982469662297</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.0009949031946715973</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1108,15 +1100,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.0004265001570010997</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1127,55 +1121,65 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0.000227793562643079</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.00212910574357388</v>
+      </c>
       <c r="F29" t="n">
-        <v>1.448577107678552e-09</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.005724326449282582</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.412860440386159e-05</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.003080792807821808</v>
+      </c>
       <c r="I29" t="n">
-        <v>4.608565549328089e-10</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.00572072862542072</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0002342583878775771</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.02314950781946659</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>0.0001698026360237932</v>
+      </c>
       <c r="E30" t="n">
-        <v>0.0005637625130154859</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5.71834062520828e-06</v>
-      </c>
+        <v>0.0001756162493430979</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>4.148322748065358e-06</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1185,12 +1189,14 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>1.157307830130374e-05</v>
+        <v>0.0006056041171712137</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>1.624516956572593e-08</v>
+      </c>
       <c r="I31" t="n">
-        <v>1.387990866727912e-05</v>
+        <v>0.0001092982469662297</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1198,7 +1204,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1207,29 +1213,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>3.021982398372452e-12</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3.531338325264679e-13</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.469299066349851e-11</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.824420290111216e-11</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.959277376230371e-13</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1.688469752281557e-10</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1238,29 +1232,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>6.371611843765214e-05</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.713496530849602e-05</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.0004995071219427</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0002751207677780113</v>
-      </c>
-      <c r="J33" t="n">
-        <v>5.557302063796528e-05</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.003510127756655649</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1270,28 +1252,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0002032153415099435</v>
-      </c>
-      <c r="G34" t="n">
-        <v>4.017227868407744e-05</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0024480240244066</v>
-      </c>
+        <v>1.448577107678552e-09</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0008140281851726</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.0001644463307791</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.01928324458791736</v>
-      </c>
+        <v>4.608565549328089e-10</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1300,19 +1274,23 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.0002818113349595355</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.0005637625130154859</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.71834062520828e-06</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>4.148322748065358e-06</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1320,20 +1298,22 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.0009826922911579049</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>1.157307830130374e-05</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>1.387990866727912e-05</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1341,25 +1321,181 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>0.001828266139132926</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
+        <v>3.021982398372452e-12</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.531338325264679e-13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.469299066349851e-11</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.824420290111216e-11</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.959277376230371e-13</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.688469752281557e-10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>6.371611843765214e-05</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.713496530849602e-05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0004995071219427</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0002751207677780113</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5.557302063796528e-05</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.003510127756655649</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0002032153415099435</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4.017227868407744e-05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0024480240244066</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0008140281851726</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0001644463307791</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.01928324458791736</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.0002818113349595355</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.0009826922911579049</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0.0001698026360237932</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.002003882388476024</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.0008898284476444115</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>5.730724434570729e-05</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.002947547406211856</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.001216475910432943</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>0.000220019351712993</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.02279337251341998</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_EE.xlsx
+++ b/Outputs/PtX_demand_EE.xlsx
@@ -501,11 +501,19 @@
       <c r="E2" t="n">
         <v>0.0001754969404269362</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.001989622805629832</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0002382038373178</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.0007320087717729001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0003223164030038</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -722,7 +730,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -731,7 +739,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0002970049348188396</v>
+        <v>0.00150444262044033</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -743,7 +751,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -752,7 +760,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.00150444262044033</v>
+        <v>0.0002970049348188396</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -799,19 +807,19 @@
         <v>0.002144104786846142</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01828014017674983</v>
+        <v>0.02026976298237966</v>
       </c>
       <c r="G15" t="n">
-        <v>4.731207815303437e-05</v>
+        <v>0.0002855159154708344</v>
       </c>
       <c r="H15" t="n">
         <v>0.003176425757448155</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01198822545005427</v>
+        <v>0.01272023422182717</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0002508564729736633</v>
+        <v>0.0005731728759774634</v>
       </c>
       <c r="K15" t="n">
         <v>0.02350081407665946</v>
@@ -833,11 +841,19 @@
       <c r="E16" t="n">
         <v>0.0001755096120484775</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.005657534471930343</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0002795541742026</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0024230831948967</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0003178788756378</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1058,7 +1074,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1067,7 +1083,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.000295424140406074</v>
+        <v>0.0009949031946715973</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1079,7 +1095,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1088,7 +1104,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.0009949031946715973</v>
+        <v>0.000295424140406074</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1135,19 +1151,19 @@
         <v>0.00212910574357388</v>
       </c>
       <c r="F29" t="n">
-        <v>0.005724326449282582</v>
+        <v>0.01138186092121292</v>
       </c>
       <c r="G29" t="n">
-        <v>5.412860440386159e-05</v>
+        <v>0.0003336827786064616</v>
       </c>
       <c r="H29" t="n">
         <v>0.003080792807821808</v>
       </c>
       <c r="I29" t="n">
-        <v>0.00572072862542072</v>
+        <v>0.008143811820317419</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0002342583878775771</v>
+        <v>0.0005521372635153771</v>
       </c>
       <c r="K29" t="n">
         <v>0.02314950781946659</v>
@@ -1169,11 +1185,19 @@
       <c r="E30" t="n">
         <v>0.0001756162493430979</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.006590272308833567</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0003139377037732</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.003527300630949</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0003246573440787</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1406,7 +1430,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1414,9 +1438,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.0002818113349595355</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1427,7 +1449,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1435,7 +1457,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.0002818113349595355</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1481,19 +1505,19 @@
         <v>0.002003882388476024</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0008898284476444115</v>
+        <v>0.007480100756477978</v>
       </c>
       <c r="G43" t="n">
-        <v>5.730724434570729e-05</v>
+        <v>0.0003712449481189073</v>
       </c>
       <c r="H43" t="n">
         <v>0.002947547406211856</v>
       </c>
       <c r="I43" t="n">
-        <v>0.001216475910432943</v>
+        <v>0.004743776541381943</v>
       </c>
       <c r="J43" t="n">
-        <v>0.000220019351712993</v>
+        <v>0.0005446766957916929</v>
       </c>
       <c r="K43" t="n">
         <v>0.02279337251341998</v>
